--- a/input/timetable/Фундаментальная и прикладная химия-.xlsx
+++ b/input/timetable/Фундаментальная и прикладная химия-.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="183">
   <si>
     <t>пара</t>
   </si>
@@ -287,9 +287,24 @@
     <t>ЭУК</t>
   </si>
   <si>
+    <t>Кузнецова А.А.</t>
+  </si>
+  <si>
+    <t>Сташкин П.Р.</t>
+  </si>
+  <si>
     <t>Безопасность жизнедеятельности (лек 32 ч)</t>
   </si>
   <si>
+    <t>Шапошникова И.В.</t>
+  </si>
+  <si>
+    <t>Логинов В.А.</t>
+  </si>
+  <si>
+    <t>Крайник В.В.</t>
+  </si>
+  <si>
     <t>Неорганическая химия (лек), А310</t>
   </si>
   <si>
@@ -305,6 +320,9 @@
     <t>302-41</t>
   </si>
   <si>
+    <t>Борисенко О.В.</t>
+  </si>
+  <si>
     <t>Физическая культура и спорт (лек 8 ч)</t>
   </si>
   <si>
@@ -323,12 +341,27 @@
     <t>Неорганическая химия, п/г 1, А121</t>
   </si>
   <si>
+    <t>Чудова Е.С.</t>
+  </si>
+  <si>
+    <t>Касьяненко-Божок Р.В.</t>
+  </si>
+  <si>
     <t>Правоведение (лек 32 ч)</t>
   </si>
   <si>
+    <t>Владимирова Г.Е.</t>
+  </si>
+  <si>
     <t>Аналитическая химия (лек), ЭОиДОТ</t>
   </si>
   <si>
+    <t>Севастьянова Е.В.</t>
+  </si>
+  <si>
+    <t>Коробкин А.В.</t>
+  </si>
+  <si>
     <t>Иностранный язык (пр), А518</t>
   </si>
   <si>
@@ -377,6 +410,24 @@
     <t>Аналитическая химия             (ТО: 02.02.2026-10.06.2026)</t>
   </si>
   <si>
+    <t>Ончева Е.М.</t>
+  </si>
+  <si>
+    <t>Шапошникова И.В./Ончева Е.М.</t>
+  </si>
+  <si>
+    <t>Сердюков Д.В.</t>
+  </si>
+  <si>
+    <t>Калинина Е.А.</t>
+  </si>
+  <si>
+    <t>Алексеев М.М.</t>
+  </si>
+  <si>
+    <t>Умарова М.М.</t>
+  </si>
+  <si>
     <t>Физика, п/г 1, А302 (с 17.00)</t>
   </si>
   <si>
@@ -416,6 +467,9 @@
     <t>Основы предпринимательской деятельности (лек 16 ч)</t>
   </si>
   <si>
+    <t>Собиров Б.Ш.</t>
+  </si>
+  <si>
     <t>Физика (лек), А314</t>
   </si>
   <si>
@@ -467,21 +521,24 @@
     <t>Органическая химия (лаб), А121</t>
   </si>
   <si>
+    <t>Теллер Е.В.</t>
+  </si>
+  <si>
     <t>Физическая химия (лек), ЭОиДОТ</t>
   </si>
   <si>
     <t>Физическая химия (пр), ЭОиДОТ</t>
   </si>
   <si>
+    <t>Мухутдинов Д.Р.</t>
+  </si>
+  <si>
     <t>Квантовая химия (лек), ЭОиДОТ</t>
   </si>
   <si>
     <t>Квантовая химия (пр), ЭОиДОТ</t>
   </si>
   <si>
-    <t>Квантовая химия (пр), ЭОиДОТ// Органическая химия (лек), ЭОиДОТ</t>
-  </si>
-  <si>
     <t>Основы экономической культуры (пр), К718</t>
   </si>
   <si>
@@ -495,6 +552,24 @@
   </si>
   <si>
     <t>Учебная практика, по получению первичных профессиональный умений и навыков, в том числе первичных умений и навыков научно-исследовательской деятельности, А310//</t>
+  </si>
+  <si>
+    <t>Петров Е.А.</t>
+  </si>
+  <si>
+    <t>Джумаева А.А. ; Петров Е.А.</t>
+  </si>
+  <si>
+    <t>Мигурская А.С.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Квантовая химия (пр), ЭОиДОТ// </t>
+  </si>
+  <si>
+    <t>//Органическая химия (лек), ЭОиДОТ</t>
+  </si>
+  <si>
+    <t>Павловский В.И.</t>
   </si>
 </sst>
 </file>
@@ -718,7 +793,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="53">
+  <borders count="54">
     <border>
       <left/>
       <right/>
@@ -1273,6 +1348,19 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -1400,7 +1488,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="231">
+  <cellXfs count="255">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -1572,18 +1660,24 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="3" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1608,6 +1702,7 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="3" borderId="2" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1618,15 +1713,17 @@
     <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1636,20 +1733,20 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1665,27 +1762,39 @@
     <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1693,95 +1802,17 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="5" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="5" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="2" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1792,11 +1823,125 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1815,53 +1960,29 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1872,107 +1993,110 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -2282,7 +2406,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P42"/>
+  <dimension ref="A1:Q42"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="52" customWidth="1"/>
@@ -2291,63 +2415,64 @@
     <col min="4" max="4" width="17.85546875" style="52" customWidth="1"/>
     <col min="5" max="5" width="18.7109375" style="52" customWidth="1"/>
     <col min="6" max="6" width="19.28515625" style="52" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="52"/>
+    <col min="7" max="7" width="18.140625" style="52" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="52"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A1" s="103" t="s">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A1" s="110" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="104"/>
-      <c r="C1" s="104"/>
-      <c r="D1" s="104"/>
-      <c r="E1" s="104"/>
-      <c r="F1" s="105" t="s">
+      <c r="B1" s="111"/>
+      <c r="C1" s="111"/>
+      <c r="D1" s="111"/>
+      <c r="E1" s="111"/>
+      <c r="F1" s="112" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A2" s="103" t="s">
-        <v>107</v>
-      </c>
-      <c r="B2" s="104"/>
-      <c r="C2" s="104"/>
-      <c r="D2" s="104"/>
-      <c r="E2" s="104"/>
-      <c r="F2" s="105" t="s">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A2" s="110" t="s">
+        <v>118</v>
+      </c>
+      <c r="B2" s="111"/>
+      <c r="C2" s="111"/>
+      <c r="D2" s="111"/>
+      <c r="E2" s="111"/>
+      <c r="F2" s="112" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A3" s="103" t="s">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A3" s="110" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="104"/>
-      <c r="C3" s="104"/>
-      <c r="D3" s="104"/>
-      <c r="E3" s="104"/>
-      <c r="F3" s="105" t="s">
+      <c r="B3" s="111"/>
+      <c r="C3" s="111"/>
+      <c r="D3" s="111"/>
+      <c r="E3" s="111"/>
+      <c r="F3" s="112" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A4" s="53" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="B4" s="54"/>
       <c r="C4" s="54"/>
       <c r="D4" s="55"/>
       <c r="E4" s="54"/>
-      <c r="F4" s="106" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="F4" s="113" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A5" s="56" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="57" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="D5" s="57"/>
       <c r="E5" s="58" t="s">
@@ -2357,442 +2482,528 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A6" s="60" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="84" t="s">
+      <c r="C6" s="89" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="84"/>
-      <c r="E6" s="85">
+      <c r="D6" s="89"/>
+      <c r="E6" s="90">
         <v>1</v>
       </c>
       <c r="F6" s="59" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:15" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="61" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="146" t="s">
+      <c r="C7" s="137" t="s">
         <v>30</v>
       </c>
-      <c r="D7" s="146"/>
-      <c r="E7" s="86" t="s">
-        <v>113</v>
+      <c r="D7" s="137"/>
+      <c r="E7" s="91" t="s">
+        <v>124</v>
       </c>
       <c r="F7" s="62" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:15" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A8" s="61" t="s">
         <v>86</v>
       </c>
-      <c r="C8" s="147" t="s">
-        <v>115</v>
-      </c>
-      <c r="D8" s="147"/>
-      <c r="E8" s="147"/>
+      <c r="C8" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="D8" s="140"/>
+      <c r="E8" s="140"/>
       <c r="F8" s="62"/>
     </row>
-    <row r="9" spans="1:14" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:15" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="63" t="s">
         <v>19</v>
       </c>
       <c r="B9" s="64" t="s">
         <v>0</v>
       </c>
-      <c r="C9" s="100" t="s">
+      <c r="C9" s="107" t="s">
         <v>1</v>
       </c>
-      <c r="D9" s="101"/>
-      <c r="E9" s="102"/>
-      <c r="F9" s="102"/>
-    </row>
-    <row r="10" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="69" t="s">
+      <c r="D9" s="108"/>
+      <c r="E9" s="109"/>
+      <c r="F9" s="109"/>
+      <c r="G9" s="69" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="70" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="70">
+      <c r="B10" s="71">
         <v>2</v>
       </c>
-      <c r="C10" s="148"/>
-      <c r="D10" s="149"/>
-      <c r="E10" s="149"/>
-      <c r="F10" s="150"/>
-    </row>
-    <row r="11" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="71"/>
-      <c r="B11" s="72">
+      <c r="C10" s="141"/>
+      <c r="D10" s="142"/>
+      <c r="E10" s="142"/>
+      <c r="F10" s="143"/>
+      <c r="G10" s="116"/>
+    </row>
+    <row r="11" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="73"/>
+      <c r="B11" s="74">
         <v>3</v>
       </c>
-      <c r="C11" s="120"/>
-      <c r="D11" s="121"/>
-      <c r="E11" s="116" t="s">
-        <v>119</v>
-      </c>
-      <c r="F11" s="117"/>
-      <c r="N11" s="91"/>
-    </row>
-    <row r="12" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="71"/>
-      <c r="B12" s="72">
+      <c r="C11" s="138"/>
+      <c r="D11" s="139"/>
+      <c r="E11" s="135" t="s">
+        <v>136</v>
+      </c>
+      <c r="F11" s="136"/>
+      <c r="G11" s="123" t="s">
+        <v>134</v>
+      </c>
+      <c r="O11" s="97"/>
+    </row>
+    <row r="12" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="73"/>
+      <c r="B12" s="74">
         <v>4</v>
       </c>
-      <c r="C12" s="115" t="s">
+      <c r="C12" s="134" t="s">
+        <v>94</v>
+      </c>
+      <c r="D12" s="135"/>
+      <c r="E12" s="135"/>
+      <c r="F12" s="136"/>
+      <c r="G12" s="122" t="s">
+        <v>93</v>
+      </c>
+      <c r="O12" s="97"/>
+    </row>
+    <row r="13" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="73"/>
+      <c r="B13" s="74">
+        <v>5</v>
+      </c>
+      <c r="C13" s="134" t="s">
+        <v>94</v>
+      </c>
+      <c r="D13" s="135"/>
+      <c r="E13" s="135"/>
+      <c r="F13" s="136"/>
+      <c r="G13" s="122" t="s">
+        <v>93</v>
+      </c>
+      <c r="O13" s="97"/>
+    </row>
+    <row r="14" spans="1:15" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="73"/>
+      <c r="B14" s="74">
+        <v>6</v>
+      </c>
+      <c r="C14" s="164" t="s">
+        <v>135</v>
+      </c>
+      <c r="D14" s="165"/>
+      <c r="E14" s="174"/>
+      <c r="F14" s="175"/>
+      <c r="G14" s="126" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="70" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="71">
+        <v>1</v>
+      </c>
+      <c r="C15" s="176"/>
+      <c r="D15" s="177"/>
+      <c r="E15" s="135" t="s">
+        <v>104</v>
+      </c>
+      <c r="F15" s="136"/>
+      <c r="G15" s="116" t="s">
+        <v>106</v>
+      </c>
+      <c r="O15" s="77"/>
+    </row>
+    <row r="16" spans="1:15" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="73"/>
+      <c r="B16" s="74">
+        <v>2</v>
+      </c>
+      <c r="C16" s="138"/>
+      <c r="D16" s="139"/>
+      <c r="E16" s="135" t="s">
+        <v>104</v>
+      </c>
+      <c r="F16" s="136"/>
+      <c r="G16" s="124" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="79"/>
+      <c r="B17" s="80">
+        <v>3</v>
+      </c>
+      <c r="C17" s="138"/>
+      <c r="D17" s="139"/>
+      <c r="E17" s="145" t="s">
+        <v>104</v>
+      </c>
+      <c r="F17" s="146"/>
+      <c r="G17" s="121" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" ht="38.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="81"/>
+      <c r="B18" s="82">
+        <v>5</v>
+      </c>
+      <c r="C18" s="152" t="s">
+        <v>97</v>
+      </c>
+      <c r="D18" s="153"/>
+      <c r="E18" s="153"/>
+      <c r="F18" s="154"/>
+      <c r="G18" s="115" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="70" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19" s="71">
+        <v>1</v>
+      </c>
+      <c r="C19" s="134" t="s">
+        <v>105</v>
+      </c>
+      <c r="D19" s="135"/>
+      <c r="E19" s="142"/>
+      <c r="F19" s="143"/>
+      <c r="G19" s="120" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="73"/>
+      <c r="B20" s="78">
+        <v>2</v>
+      </c>
+      <c r="C20" s="134" t="s">
+        <v>105</v>
+      </c>
+      <c r="D20" s="135"/>
+      <c r="E20" s="147"/>
+      <c r="F20" s="148"/>
+      <c r="G20" s="119" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="73"/>
+      <c r="B21" s="78">
+        <v>3</v>
+      </c>
+      <c r="C21" s="134" t="s">
+        <v>105</v>
+      </c>
+      <c r="D21" s="135"/>
+      <c r="E21" s="147"/>
+      <c r="F21" s="148"/>
+      <c r="G21" s="117" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="79"/>
+      <c r="B22" s="80">
+        <v>4</v>
+      </c>
+      <c r="C22" s="161" t="s">
+        <v>138</v>
+      </c>
+      <c r="D22" s="162"/>
+      <c r="E22" s="162"/>
+      <c r="F22" s="163"/>
+      <c r="G22" s="125" t="s">
         <v>89</v>
       </c>
-      <c r="D12" s="116"/>
-      <c r="E12" s="116"/>
-      <c r="F12" s="117"/>
-      <c r="N12" s="91"/>
-    </row>
-    <row r="13" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="71"/>
-      <c r="B13" s="72">
+      <c r="Q22" s="77"/>
+    </row>
+    <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="70" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23" s="71">
+        <v>1</v>
+      </c>
+      <c r="C23" s="149" t="s">
+        <v>139</v>
+      </c>
+      <c r="D23" s="150"/>
+      <c r="E23" s="150"/>
+      <c r="F23" s="151"/>
+      <c r="G23" s="116" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="73"/>
+      <c r="B24" s="78">
+        <v>2</v>
+      </c>
+      <c r="C24" s="144" t="s">
+        <v>140</v>
+      </c>
+      <c r="D24" s="145"/>
+      <c r="E24" s="145"/>
+      <c r="F24" s="146"/>
+      <c r="G24" s="122" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="73"/>
+      <c r="B25" s="74">
+        <v>3</v>
+      </c>
+      <c r="C25" s="144" t="s">
+        <v>141</v>
+      </c>
+      <c r="D25" s="145"/>
+      <c r="E25" s="145"/>
+      <c r="F25" s="146"/>
+      <c r="G25" s="121" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="81"/>
+      <c r="B26" s="82">
+        <v>4</v>
+      </c>
+      <c r="C26" s="164" t="s">
+        <v>146</v>
+      </c>
+      <c r="D26" s="165"/>
+      <c r="E26" s="165"/>
+      <c r="F26" s="166"/>
+      <c r="G26" s="126" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="70" t="s">
+        <v>24</v>
+      </c>
+      <c r="B27" s="71">
+        <v>1</v>
+      </c>
+      <c r="C27" s="158" t="s">
+        <v>142</v>
+      </c>
+      <c r="D27" s="159"/>
+      <c r="E27" s="159"/>
+      <c r="F27" s="160"/>
+      <c r="G27" s="116" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="83"/>
+      <c r="B28" s="74">
+        <v>2</v>
+      </c>
+      <c r="C28" s="144" t="s">
+        <v>143</v>
+      </c>
+      <c r="D28" s="145"/>
+      <c r="E28" s="145"/>
+      <c r="F28" s="146"/>
+      <c r="G28" s="122" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="83"/>
+      <c r="B29" s="74">
+        <v>3</v>
+      </c>
+      <c r="C29" s="134" t="s">
+        <v>144</v>
+      </c>
+      <c r="D29" s="135"/>
+      <c r="E29" s="135"/>
+      <c r="F29" s="136"/>
+      <c r="G29" s="122" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="84"/>
+      <c r="B30" s="80">
+        <v>4</v>
+      </c>
+      <c r="C30" s="144" t="s">
+        <v>145</v>
+      </c>
+      <c r="D30" s="145"/>
+      <c r="E30" s="145"/>
+      <c r="F30" s="146"/>
+      <c r="G30" s="117" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A31" s="84"/>
+      <c r="B31" s="80">
         <v>5</v>
       </c>
-      <c r="C13" s="115" t="s">
-        <v>89</v>
-      </c>
-      <c r="D13" s="116"/>
-      <c r="E13" s="116"/>
-      <c r="F13" s="117"/>
-      <c r="N13" s="91"/>
-    </row>
-    <row r="14" spans="1:14" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="71"/>
-      <c r="B14" s="72">
-        <v>6</v>
-      </c>
-      <c r="C14" s="124" t="s">
-        <v>118</v>
-      </c>
-      <c r="D14" s="125"/>
-      <c r="E14" s="113"/>
-      <c r="F14" s="114"/>
-    </row>
-    <row r="15" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="69" t="s">
-        <v>21</v>
-      </c>
-      <c r="B15" s="70">
+      <c r="C31" s="167"/>
+      <c r="D31" s="168"/>
+      <c r="E31" s="168"/>
+      <c r="F31" s="169"/>
+      <c r="G31" s="85"/>
+    </row>
+    <row r="32" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="86" t="s">
+        <v>25</v>
+      </c>
+      <c r="B32" s="71">
         <v>1</v>
       </c>
-      <c r="C15" s="118"/>
-      <c r="D15" s="119"/>
-      <c r="E15" s="116" t="s">
-        <v>98</v>
-      </c>
-      <c r="F15" s="117"/>
-      <c r="N15" s="73"/>
-    </row>
-    <row r="16" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="71"/>
-      <c r="B16" s="72">
-        <v>2</v>
-      </c>
-      <c r="C16" s="120"/>
-      <c r="D16" s="121"/>
-      <c r="E16" s="116" t="s">
-        <v>98</v>
-      </c>
-      <c r="F16" s="117"/>
-    </row>
-    <row r="17" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="75"/>
-      <c r="B17" s="76">
+      <c r="C32" s="170" t="s">
+        <v>96</v>
+      </c>
+      <c r="D32" s="171"/>
+      <c r="E32" s="171"/>
+      <c r="F32" s="172"/>
+      <c r="G32" s="116" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="87"/>
+      <c r="B33" s="78">
         <v>3</v>
       </c>
-      <c r="C17" s="120"/>
-      <c r="D17" s="121"/>
-      <c r="E17" s="122" t="s">
-        <v>98</v>
-      </c>
-      <c r="F17" s="123"/>
-    </row>
-    <row r="18" spans="1:16" ht="38.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="77"/>
-      <c r="B18" s="78">
+      <c r="C33" s="134" t="s">
+        <v>137</v>
+      </c>
+      <c r="D33" s="135"/>
+      <c r="E33" s="135" t="s">
+        <v>103</v>
+      </c>
+      <c r="F33" s="136"/>
+      <c r="G33" s="122" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A34" s="87"/>
+      <c r="B34" s="74">
+        <v>4</v>
+      </c>
+      <c r="C34" s="173"/>
+      <c r="D34" s="147"/>
+      <c r="E34" s="147"/>
+      <c r="F34" s="148"/>
+      <c r="G34" s="123"/>
+    </row>
+    <row r="35" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A35" s="87"/>
+      <c r="B35" s="74">
         <v>5</v>
       </c>
-      <c r="C18" s="110" t="s">
-        <v>92</v>
-      </c>
-      <c r="D18" s="111"/>
-      <c r="E18" s="111"/>
-      <c r="F18" s="112"/>
-    </row>
-    <row r="19" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="69" t="s">
-        <v>22</v>
-      </c>
-      <c r="B19" s="70">
-        <v>1</v>
-      </c>
-      <c r="C19" s="115" t="s">
+      <c r="C35" s="173"/>
+      <c r="D35" s="147"/>
+      <c r="E35" s="147"/>
+      <c r="F35" s="148"/>
+      <c r="G35" s="122"/>
+      <c r="H35" s="97"/>
+    </row>
+    <row r="36" spans="1:8" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A36" s="94"/>
+      <c r="B36" s="95"/>
+      <c r="C36" s="155"/>
+      <c r="D36" s="156"/>
+      <c r="E36" s="156"/>
+      <c r="F36" s="157"/>
+      <c r="G36" s="96"/>
+    </row>
+    <row r="37" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A37" s="99"/>
+      <c r="B37" s="102" t="s">
+        <v>87</v>
+      </c>
+      <c r="C37" s="158" t="s">
+        <v>90</v>
+      </c>
+      <c r="D37" s="159"/>
+      <c r="E37" s="159"/>
+      <c r="F37" s="160"/>
+      <c r="G37" s="120" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A38" s="100"/>
+      <c r="B38" s="103" t="s">
+        <v>87</v>
+      </c>
+      <c r="C38" s="144" t="s">
+        <v>100</v>
+      </c>
+      <c r="D38" s="145"/>
+      <c r="E38" s="145"/>
+      <c r="F38" s="146"/>
+      <c r="G38" s="117" t="s">
         <v>99</v>
       </c>
-      <c r="D19" s="116"/>
-      <c r="E19" s="149"/>
-      <c r="F19" s="150"/>
-    </row>
-    <row r="20" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="71"/>
-      <c r="B20" s="74">
-        <v>2</v>
-      </c>
-      <c r="C20" s="115" t="s">
-        <v>99</v>
-      </c>
-      <c r="D20" s="116"/>
-      <c r="E20" s="144"/>
-      <c r="F20" s="145"/>
-    </row>
-    <row r="21" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="71"/>
-      <c r="B21" s="74">
-        <v>3</v>
-      </c>
-      <c r="C21" s="115" t="s">
-        <v>99</v>
-      </c>
-      <c r="D21" s="116"/>
-      <c r="E21" s="144"/>
-      <c r="F21" s="145"/>
-    </row>
-    <row r="22" spans="1:16" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="75"/>
-      <c r="B22" s="76">
-        <v>4</v>
-      </c>
-      <c r="C22" s="132" t="s">
-        <v>121</v>
-      </c>
-      <c r="D22" s="133"/>
-      <c r="E22" s="133"/>
-      <c r="F22" s="134"/>
-      <c r="P22" s="73"/>
-    </row>
-    <row r="23" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="69" t="s">
-        <v>23</v>
-      </c>
-      <c r="B23" s="70">
-        <v>1</v>
-      </c>
-      <c r="C23" s="151" t="s">
-        <v>122</v>
-      </c>
-      <c r="D23" s="152"/>
-      <c r="E23" s="152"/>
-      <c r="F23" s="153"/>
-    </row>
-    <row r="24" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="71"/>
-      <c r="B24" s="74">
-        <v>2</v>
-      </c>
-      <c r="C24" s="135" t="s">
-        <v>123</v>
-      </c>
-      <c r="D24" s="122"/>
-      <c r="E24" s="122"/>
-      <c r="F24" s="123"/>
-    </row>
-    <row r="25" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="71"/>
-      <c r="B25" s="72">
-        <v>3</v>
-      </c>
-      <c r="C25" s="135" t="s">
-        <v>124</v>
-      </c>
-      <c r="D25" s="122"/>
-      <c r="E25" s="122"/>
-      <c r="F25" s="123"/>
-    </row>
-    <row r="26" spans="1:16" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A26" s="77"/>
-      <c r="B26" s="78">
-        <v>4</v>
-      </c>
-      <c r="C26" s="124" t="s">
-        <v>129</v>
-      </c>
-      <c r="D26" s="125"/>
-      <c r="E26" s="125"/>
-      <c r="F26" s="136"/>
-    </row>
-    <row r="27" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="69" t="s">
-        <v>24</v>
-      </c>
-      <c r="B27" s="70">
-        <v>1</v>
-      </c>
-      <c r="C27" s="129" t="s">
-        <v>125</v>
-      </c>
-      <c r="D27" s="130"/>
-      <c r="E27" s="130"/>
-      <c r="F27" s="131"/>
-    </row>
-    <row r="28" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="79"/>
-      <c r="B28" s="72">
-        <v>2</v>
-      </c>
-      <c r="C28" s="135" t="s">
-        <v>126</v>
-      </c>
-      <c r="D28" s="122"/>
-      <c r="E28" s="122"/>
-      <c r="F28" s="123"/>
-    </row>
-    <row r="29" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="79"/>
-      <c r="B29" s="72">
-        <v>3</v>
-      </c>
-      <c r="C29" s="115" t="s">
-        <v>127</v>
-      </c>
-      <c r="D29" s="116"/>
-      <c r="E29" s="116"/>
-      <c r="F29" s="117"/>
-    </row>
-    <row r="30" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="80"/>
-      <c r="B30" s="76">
-        <v>4</v>
-      </c>
-      <c r="C30" s="135" t="s">
-        <v>128</v>
-      </c>
-      <c r="D30" s="122"/>
-      <c r="E30" s="122"/>
-      <c r="F30" s="123"/>
-    </row>
-    <row r="31" spans="1:16" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A31" s="80"/>
-      <c r="B31" s="76">
-        <v>5</v>
-      </c>
-      <c r="C31" s="137"/>
-      <c r="D31" s="138"/>
-      <c r="E31" s="138"/>
-      <c r="F31" s="139"/>
-    </row>
-    <row r="32" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="81" t="s">
-        <v>25</v>
-      </c>
-      <c r="B32" s="70">
-        <v>1</v>
-      </c>
-      <c r="C32" s="140" t="s">
-        <v>91</v>
-      </c>
-      <c r="D32" s="141"/>
-      <c r="E32" s="141"/>
-      <c r="F32" s="142"/>
-    </row>
-    <row r="33" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="82"/>
-      <c r="B33" s="74">
-        <v>3</v>
-      </c>
-      <c r="C33" s="115" t="s">
-        <v>120</v>
-      </c>
-      <c r="D33" s="116"/>
-      <c r="E33" s="116" t="s">
-        <v>97</v>
-      </c>
-      <c r="F33" s="117"/>
-    </row>
-    <row r="34" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="82"/>
-      <c r="B34" s="72">
-        <v>4</v>
-      </c>
-      <c r="C34" s="143"/>
-      <c r="D34" s="144"/>
-      <c r="E34" s="144"/>
-      <c r="F34" s="145"/>
-    </row>
-    <row r="35" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="82"/>
-      <c r="B35" s="72">
-        <v>5</v>
-      </c>
-      <c r="C35" s="143"/>
-      <c r="D35" s="144"/>
-      <c r="E35" s="144"/>
-      <c r="F35" s="145"/>
-      <c r="G35" s="91"/>
-    </row>
-    <row r="36" spans="1:7" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A36" s="89"/>
-      <c r="B36" s="90"/>
-      <c r="C36" s="126"/>
-      <c r="D36" s="127"/>
-      <c r="E36" s="127"/>
-      <c r="F36" s="128"/>
-    </row>
-    <row r="37" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="92"/>
-      <c r="B37" s="95" t="s">
+    </row>
+    <row r="39" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A39" s="105"/>
+      <c r="B39" s="106" t="s">
         <v>87</v>
       </c>
-      <c r="C37" s="129" t="s">
+      <c r="C39" s="144" t="s">
+        <v>102</v>
+      </c>
+      <c r="D39" s="145"/>
+      <c r="E39" s="145"/>
+      <c r="F39" s="146"/>
+      <c r="G39" s="121" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A40" s="101"/>
+      <c r="B40" s="104" t="s">
+        <v>87</v>
+      </c>
+      <c r="C40" s="152" t="s">
+        <v>101</v>
+      </c>
+      <c r="D40" s="153"/>
+      <c r="E40" s="153"/>
+      <c r="F40" s="154"/>
+      <c r="G40" s="118" t="s">
         <v>88</v>
       </c>
-      <c r="D37" s="130"/>
-      <c r="E37" s="130"/>
-      <c r="F37" s="131"/>
-    </row>
-    <row r="38" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A38" s="93"/>
-      <c r="B38" s="96" t="s">
-        <v>87</v>
-      </c>
-      <c r="C38" s="135" t="s">
-        <v>94</v>
-      </c>
-      <c r="D38" s="122"/>
-      <c r="E38" s="122"/>
-      <c r="F38" s="123"/>
-    </row>
-    <row r="39" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="98"/>
-      <c r="B39" s="99" t="s">
-        <v>87</v>
-      </c>
-      <c r="C39" s="135" t="s">
-        <v>96</v>
-      </c>
-      <c r="D39" s="122"/>
-      <c r="E39" s="122"/>
-      <c r="F39" s="123"/>
-    </row>
-    <row r="40" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A40" s="94"/>
-      <c r="B40" s="97" t="s">
-        <v>87</v>
-      </c>
-      <c r="C40" s="110" t="s">
-        <v>95</v>
-      </c>
-      <c r="D40" s="111"/>
-      <c r="E40" s="111"/>
-      <c r="F40" s="112"/>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.4">
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.4">
       <c r="B41" s="52" t="s">
         <v>14</v>
       </c>
@@ -2800,16 +3011,42 @@
         <v>17</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.4">
       <c r="B42" s="52" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="E42" s="52" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="42">
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C40:F40"/>
+    <mergeCell ref="C36:F36"/>
+    <mergeCell ref="C37:F37"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="C38:F38"/>
+    <mergeCell ref="C39:F39"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="C29:F29"/>
     <mergeCell ref="C33:D33"/>
     <mergeCell ref="E33:F33"/>
     <mergeCell ref="C7:D7"/>
@@ -2826,32 +3063,6 @@
     <mergeCell ref="E21:F21"/>
     <mergeCell ref="C23:F23"/>
     <mergeCell ref="C12:F12"/>
-    <mergeCell ref="C40:F40"/>
-    <mergeCell ref="C36:F36"/>
-    <mergeCell ref="C37:F37"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C26:F26"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C31:F31"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="C38:F38"/>
-    <mergeCell ref="C39:F39"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="C34:F34"/>
-    <mergeCell ref="C35:F35"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="C18:F18"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="C13:F13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="C14:D14"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" sqref="C6"/>
@@ -2869,7 +3080,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J39"/>
+  <dimension ref="A1:K40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.85546875" customWidth="1"/>
@@ -2877,63 +3088,68 @@
     <col min="3" max="3" width="20" customWidth="1"/>
     <col min="4" max="5" width="16.140625" customWidth="1"/>
     <col min="6" max="6" width="17.5703125" customWidth="1"/>
+    <col min="7" max="7" width="18.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18.75" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A1" s="51" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="104"/>
-      <c r="C1" s="104"/>
-      <c r="D1" s="104"/>
-      <c r="E1" s="104"/>
-      <c r="F1" s="105" t="s">
+      <c r="B1" s="111"/>
+      <c r="C1" s="111"/>
+      <c r="D1" s="111"/>
+      <c r="E1" s="111"/>
+      <c r="F1" s="112" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" ht="18.75" x14ac:dyDescent="0.35">
+      <c r="G1" s="52"/>
+    </row>
+    <row r="2" spans="1:11" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A2" s="51" t="s">
-        <v>107</v>
-      </c>
-      <c r="B2" s="104"/>
-      <c r="C2" s="104"/>
-      <c r="D2" s="104"/>
-      <c r="E2" s="104"/>
-      <c r="F2" s="105" t="s">
+        <v>118</v>
+      </c>
+      <c r="B2" s="111"/>
+      <c r="C2" s="111"/>
+      <c r="D2" s="111"/>
+      <c r="E2" s="111"/>
+      <c r="F2" s="112" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" ht="18.75" x14ac:dyDescent="0.35">
+      <c r="G2" s="52"/>
+    </row>
+    <row r="3" spans="1:11" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A3" s="51" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="104"/>
-      <c r="C3" s="104"/>
-      <c r="D3" s="104"/>
-      <c r="E3" s="104"/>
-      <c r="F3" s="105" t="s">
+      <c r="B3" s="111"/>
+      <c r="C3" s="111"/>
+      <c r="D3" s="111"/>
+      <c r="E3" s="111"/>
+      <c r="F3" s="112" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="G3" s="52"/>
+    </row>
+    <row r="4" spans="1:11" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A4" s="53" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="B4" s="54"/>
       <c r="C4" s="54"/>
       <c r="D4" s="55"/>
       <c r="E4" s="54"/>
-      <c r="F4" s="106" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="F4" s="113" t="s">
+        <v>123</v>
+      </c>
+      <c r="G4" s="52"/>
+    </row>
+    <row r="5" spans="1:11" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A5" s="56" t="s">
         <v>2</v>
       </c>
       <c r="B5" s="52"/>
       <c r="C5" s="57" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="D5" s="57"/>
       <c r="E5" s="58" t="s">
@@ -2942,55 +3158,59 @@
       <c r="F5" s="59" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="G5" s="52"/>
+    </row>
+    <row r="6" spans="1:11" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A6" s="60" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="52"/>
-      <c r="C6" s="84" t="s">
+      <c r="C6" s="89" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="84"/>
-      <c r="E6" s="85">
+      <c r="D6" s="89"/>
+      <c r="E6" s="90">
         <v>2</v>
       </c>
       <c r="F6" s="59" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="G6" s="52"/>
+    </row>
+    <row r="7" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="61" t="s">
         <v>26</v>
       </c>
       <c r="B7" s="52"/>
-      <c r="C7" s="146" t="s">
+      <c r="C7" s="137" t="s">
         <v>30</v>
       </c>
-      <c r="D7" s="146"/>
-      <c r="E7" s="107" t="s">
-        <v>93</v>
+      <c r="D7" s="137"/>
+      <c r="E7" s="114" t="s">
+        <v>98</v>
       </c>
       <c r="F7" s="62" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="G7" s="52"/>
+    </row>
+    <row r="8" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A8" s="61" t="s">
         <v>86</v>
       </c>
       <c r="B8" s="52"/>
-      <c r="C8" s="147" t="s">
-        <v>116</v>
-      </c>
-      <c r="D8" s="147"/>
-      <c r="E8" s="147"/>
+      <c r="C8" s="140" t="s">
+        <v>127</v>
+      </c>
+      <c r="D8" s="140"/>
+      <c r="E8" s="140"/>
       <c r="F8" s="62"/>
-      <c r="J8" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="G8" s="52"/>
+      <c r="K8" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="63" t="s">
         <v>19</v>
       </c>
@@ -3003,387 +3223,453 @@
       <c r="D9" s="66"/>
       <c r="E9" s="67"/>
       <c r="F9" s="68"/>
-    </row>
-    <row r="10" spans="1:10" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A10" s="69" t="s">
+      <c r="G9" s="69" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A10" s="70" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="70">
+      <c r="B10" s="71">
         <v>1</v>
       </c>
-      <c r="C10" s="154" t="s">
-        <v>102</v>
-      </c>
-      <c r="D10" s="155"/>
-      <c r="E10" s="155"/>
-      <c r="F10" s="156"/>
-    </row>
-    <row r="11" spans="1:10" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A11" s="71"/>
-      <c r="B11" s="72">
+      <c r="C10" s="185" t="s">
+        <v>113</v>
+      </c>
+      <c r="D10" s="186"/>
+      <c r="E10" s="186"/>
+      <c r="F10" s="187"/>
+      <c r="G10" s="120" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A11" s="73"/>
+      <c r="B11" s="74">
         <v>2</v>
       </c>
-      <c r="C11" s="143"/>
-      <c r="D11" s="144"/>
-      <c r="E11" s="144"/>
-      <c r="F11" s="145"/>
-    </row>
-    <row r="12" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="71"/>
-      <c r="B12" s="72">
+      <c r="C11" s="173"/>
+      <c r="D11" s="147"/>
+      <c r="E11" s="147"/>
+      <c r="F11" s="148"/>
+      <c r="G11" s="129"/>
+    </row>
+    <row r="12" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="73"/>
+      <c r="B12" s="74">
         <v>3</v>
       </c>
-      <c r="C12" s="135" t="s">
+      <c r="C12" s="144" t="s">
+        <v>96</v>
+      </c>
+      <c r="D12" s="145"/>
+      <c r="E12" s="145"/>
+      <c r="F12" s="146"/>
+      <c r="G12" s="98"/>
+    </row>
+    <row r="13" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A13" s="73"/>
+      <c r="B13" s="74"/>
+      <c r="C13" s="188"/>
+      <c r="D13" s="189"/>
+      <c r="E13" s="189"/>
+      <c r="F13" s="190"/>
+      <c r="G13" s="123"/>
+    </row>
+    <row r="14" spans="1:11" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A14" s="70" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="71">
+        <v>1</v>
+      </c>
+      <c r="C14" s="191" t="s">
+        <v>149</v>
+      </c>
+      <c r="D14" s="192"/>
+      <c r="E14" s="192"/>
+      <c r="F14" s="193"/>
+      <c r="G14" s="116" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A15" s="73"/>
+      <c r="B15" s="78">
+        <v>2</v>
+      </c>
+      <c r="C15" s="194" t="s">
+        <v>116</v>
+      </c>
+      <c r="D15" s="195"/>
+      <c r="E15" s="195"/>
+      <c r="F15" s="196"/>
+      <c r="G15" s="122" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A16" s="73"/>
+      <c r="B16" s="74">
+        <v>3</v>
+      </c>
+      <c r="C16" s="144" t="s">
+        <v>153</v>
+      </c>
+      <c r="D16" s="145"/>
+      <c r="E16" s="145"/>
+      <c r="F16" s="146"/>
+      <c r="G16" s="124" t="s">
         <v>91</v>
       </c>
-      <c r="D12" s="122"/>
-      <c r="E12" s="122"/>
-      <c r="F12" s="123"/>
-    </row>
-    <row r="13" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="71"/>
-      <c r="B13" s="72"/>
-      <c r="C13" s="157"/>
-      <c r="D13" s="158"/>
-      <c r="E13" s="158"/>
-      <c r="F13" s="159"/>
-    </row>
-    <row r="14" spans="1:10" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A14" s="69" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" s="70">
+    </row>
+    <row r="17" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A17" s="81"/>
+      <c r="B17" s="82">
+        <v>4</v>
+      </c>
+      <c r="C17" s="144" t="s">
+        <v>114</v>
+      </c>
+      <c r="D17" s="145"/>
+      <c r="E17" s="145"/>
+      <c r="F17" s="146"/>
+      <c r="G17" s="122" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="70" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" s="71">
+        <v>3</v>
+      </c>
+      <c r="C18" s="158" t="s">
+        <v>154</v>
+      </c>
+      <c r="D18" s="159"/>
+      <c r="E18" s="159"/>
+      <c r="F18" s="160"/>
+      <c r="G18" s="116" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="73"/>
+      <c r="B19" s="78">
+        <v>4</v>
+      </c>
+      <c r="C19" s="181" t="s">
+        <v>154</v>
+      </c>
+      <c r="D19" s="182"/>
+      <c r="E19" s="182"/>
+      <c r="F19" s="183"/>
+      <c r="G19" s="122" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="73"/>
+      <c r="B20" s="78">
+        <v>5</v>
+      </c>
+      <c r="C20" s="144"/>
+      <c r="D20" s="145"/>
+      <c r="E20" s="145"/>
+      <c r="F20" s="146"/>
+      <c r="G20" s="122"/>
+    </row>
+    <row r="21" spans="1:7" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A21" s="73"/>
+      <c r="B21" s="74">
+        <v>6</v>
+      </c>
+      <c r="C21" s="144"/>
+      <c r="D21" s="145"/>
+      <c r="E21" s="145"/>
+      <c r="F21" s="146"/>
+      <c r="G21" s="129"/>
+    </row>
+    <row r="22" spans="1:7" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A22" s="70" t="s">
+        <v>23</v>
+      </c>
+      <c r="B22" s="71">
         <v>1</v>
       </c>
-      <c r="C14" s="160" t="s">
-        <v>131</v>
-      </c>
-      <c r="D14" s="161"/>
-      <c r="E14" s="161"/>
-      <c r="F14" s="162"/>
-    </row>
-    <row r="15" spans="1:10" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A15" s="71"/>
-      <c r="B15" s="74">
+      <c r="C22" s="184" t="s">
+        <v>155</v>
+      </c>
+      <c r="D22" s="159"/>
+      <c r="E22" s="159"/>
+      <c r="F22" s="160"/>
+      <c r="G22" s="116" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A23" s="73"/>
+      <c r="B23" s="78">
         <v>2</v>
       </c>
-      <c r="C15" s="163" t="s">
-        <v>105</v>
-      </c>
-      <c r="D15" s="164"/>
-      <c r="E15" s="164"/>
-      <c r="F15" s="165"/>
-    </row>
-    <row r="16" spans="1:10" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A16" s="71"/>
-      <c r="B16" s="72">
+      <c r="C23" s="144" t="s">
+        <v>156</v>
+      </c>
+      <c r="D23" s="145"/>
+      <c r="E23" s="145"/>
+      <c r="F23" s="146"/>
+      <c r="G23" s="122" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A24" s="73"/>
+      <c r="B24" s="74">
         <v>3</v>
       </c>
-      <c r="C16" s="135" t="s">
-        <v>135</v>
-      </c>
-      <c r="D16" s="122"/>
-      <c r="E16" s="122"/>
-      <c r="F16" s="123"/>
-    </row>
-    <row r="17" spans="1:6" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A17" s="77"/>
-      <c r="B17" s="78">
+      <c r="C24" s="144" t="s">
+        <v>96</v>
+      </c>
+      <c r="D24" s="145"/>
+      <c r="E24" s="145"/>
+      <c r="F24" s="146"/>
+      <c r="G24" s="75"/>
+    </row>
+    <row r="25" spans="1:7" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="79"/>
+      <c r="B25" s="80">
+        <v>5</v>
+      </c>
+      <c r="C25" s="144" t="s">
+        <v>151</v>
+      </c>
+      <c r="D25" s="145"/>
+      <c r="E25" s="145"/>
+      <c r="F25" s="146"/>
+      <c r="G25" s="122" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="38.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="81"/>
+      <c r="B26" s="82">
+        <v>6</v>
+      </c>
+      <c r="C26" s="144" t="s">
+        <v>152</v>
+      </c>
+      <c r="D26" s="145"/>
+      <c r="E26" s="145"/>
+      <c r="F26" s="146"/>
+      <c r="G26" s="129" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A27" s="70" t="s">
+        <v>24</v>
+      </c>
+      <c r="B27" s="71">
+        <v>1</v>
+      </c>
+      <c r="C27" s="158" t="s">
+        <v>157</v>
+      </c>
+      <c r="D27" s="159"/>
+      <c r="E27" s="159"/>
+      <c r="F27" s="160"/>
+      <c r="G27" s="116" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A28" s="83"/>
+      <c r="B28" s="74">
+        <v>2</v>
+      </c>
+      <c r="C28" s="144" t="s">
+        <v>115</v>
+      </c>
+      <c r="D28" s="145"/>
+      <c r="E28" s="145"/>
+      <c r="F28" s="146"/>
+      <c r="G28" s="122" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A29" s="83"/>
+      <c r="B29" s="74">
+        <v>3</v>
+      </c>
+      <c r="C29" s="144"/>
+      <c r="D29" s="145"/>
+      <c r="E29" s="145"/>
+      <c r="F29" s="146"/>
+      <c r="G29" s="122"/>
+    </row>
+    <row r="30" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="84"/>
+      <c r="B30" s="80">
         <v>4</v>
       </c>
-      <c r="C17" s="135" t="s">
-        <v>103</v>
-      </c>
-      <c r="D17" s="122"/>
-      <c r="E17" s="122"/>
-      <c r="F17" s="123"/>
-    </row>
-    <row r="18" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="69" t="s">
-        <v>22</v>
-      </c>
-      <c r="B18" s="70">
-        <v>3</v>
-      </c>
-      <c r="C18" s="129" t="s">
-        <v>136</v>
-      </c>
-      <c r="D18" s="130"/>
-      <c r="E18" s="130"/>
-      <c r="F18" s="131"/>
-    </row>
-    <row r="19" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="71"/>
-      <c r="B19" s="74">
+      <c r="C30" s="144" t="s">
+        <v>110</v>
+      </c>
+      <c r="D30" s="145"/>
+      <c r="E30" s="145"/>
+      <c r="F30" s="146"/>
+      <c r="G30" s="122" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A31" s="84"/>
+      <c r="B31" s="80">
+        <v>5</v>
+      </c>
+      <c r="C31" s="178" t="s">
+        <v>110</v>
+      </c>
+      <c r="D31" s="179"/>
+      <c r="E31" s="179"/>
+      <c r="F31" s="180"/>
+      <c r="G31" s="115" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A32" s="86" t="s">
+        <v>25</v>
+      </c>
+      <c r="B32" s="71">
+        <v>1</v>
+      </c>
+      <c r="C32" s="158" t="s">
+        <v>150</v>
+      </c>
+      <c r="D32" s="159"/>
+      <c r="E32" s="159"/>
+      <c r="F32" s="160"/>
+      <c r="G32" s="116" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A33" s="87"/>
+      <c r="B33" s="78">
         <v>4</v>
       </c>
-      <c r="C19" s="166" t="s">
-        <v>136</v>
-      </c>
-      <c r="D19" s="167"/>
-      <c r="E19" s="167"/>
-      <c r="F19" s="168"/>
-    </row>
-    <row r="20" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="71"/>
-      <c r="B20" s="74">
+      <c r="C33" s="144" t="s">
+        <v>117</v>
+      </c>
+      <c r="D33" s="145"/>
+      <c r="E33" s="145"/>
+      <c r="F33" s="146"/>
+      <c r="G33" s="122" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A34" s="87"/>
+      <c r="B34" s="74">
+        <v>5</v>
+      </c>
+      <c r="C34" s="144" t="s">
+        <v>117</v>
+      </c>
+      <c r="D34" s="145"/>
+      <c r="E34" s="145"/>
+      <c r="F34" s="146"/>
+      <c r="G34" s="123" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A35" s="87"/>
+      <c r="B35" s="74">
         <v>6</v>
       </c>
-      <c r="C20" s="135" t="s">
-        <v>133</v>
-      </c>
-      <c r="D20" s="122"/>
-      <c r="E20" s="122"/>
-      <c r="F20" s="123"/>
-    </row>
-    <row r="21" spans="1:6" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A21" s="71"/>
-      <c r="B21" s="72">
-        <v>7</v>
-      </c>
-      <c r="C21" s="135" t="s">
-        <v>134</v>
-      </c>
-      <c r="D21" s="122"/>
-      <c r="E21" s="122"/>
-      <c r="F21" s="123"/>
-    </row>
-    <row r="22" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A22" s="69" t="s">
-        <v>23</v>
-      </c>
-      <c r="B22" s="70">
-        <v>1</v>
-      </c>
-      <c r="C22" s="169" t="s">
-        <v>137</v>
-      </c>
-      <c r="D22" s="130"/>
-      <c r="E22" s="130"/>
-      <c r="F22" s="131"/>
-    </row>
-    <row r="23" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A23" s="71"/>
-      <c r="B23" s="74">
-        <v>2</v>
-      </c>
-      <c r="C23" s="135" t="s">
-        <v>138</v>
-      </c>
-      <c r="D23" s="122"/>
-      <c r="E23" s="122"/>
-      <c r="F23" s="123"/>
-    </row>
-    <row r="24" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A24" s="71"/>
-      <c r="B24" s="72">
-        <v>3</v>
-      </c>
-      <c r="C24" s="135" t="s">
-        <v>91</v>
-      </c>
-      <c r="D24" s="122"/>
-      <c r="E24" s="122"/>
-      <c r="F24" s="123"/>
-    </row>
-    <row r="25" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A25" s="77"/>
-      <c r="B25" s="78">
-        <v>5</v>
-      </c>
-      <c r="C25" s="110" t="s">
-        <v>132</v>
-      </c>
-      <c r="D25" s="111"/>
-      <c r="E25" s="111"/>
-      <c r="F25" s="112"/>
-    </row>
-    <row r="26" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A26" s="69" t="s">
-        <v>24</v>
-      </c>
-      <c r="B26" s="70">
-        <v>1</v>
-      </c>
-      <c r="C26" s="129" t="s">
-        <v>139</v>
-      </c>
-      <c r="D26" s="130"/>
-      <c r="E26" s="130"/>
-      <c r="F26" s="131"/>
-    </row>
-    <row r="27" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A27" s="79"/>
-      <c r="B27" s="72">
-        <v>2</v>
-      </c>
-      <c r="C27" s="135" t="s">
-        <v>104</v>
-      </c>
-      <c r="D27" s="122"/>
-      <c r="E27" s="122"/>
-      <c r="F27" s="123"/>
-    </row>
-    <row r="28" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A28" s="79"/>
-      <c r="B28" s="72">
-        <v>3</v>
-      </c>
-      <c r="C28" s="135"/>
-      <c r="D28" s="122"/>
-      <c r="E28" s="122"/>
-      <c r="F28" s="123"/>
-    </row>
-    <row r="29" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="80"/>
-      <c r="B29" s="76">
-        <v>4</v>
-      </c>
-      <c r="C29" s="135" t="s">
-        <v>101</v>
-      </c>
-      <c r="D29" s="122"/>
-      <c r="E29" s="122"/>
-      <c r="F29" s="123"/>
-    </row>
-    <row r="30" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="80"/>
-      <c r="B30" s="76">
-        <v>5</v>
-      </c>
-      <c r="C30" s="170" t="s">
-        <v>101</v>
-      </c>
-      <c r="D30" s="171"/>
-      <c r="E30" s="171"/>
-      <c r="F30" s="172"/>
-    </row>
-    <row r="31" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A31" s="81" t="s">
-        <v>25</v>
-      </c>
-      <c r="B31" s="70">
-        <v>3</v>
-      </c>
-      <c r="C31" s="148"/>
-      <c r="D31" s="149"/>
-      <c r="E31" s="149"/>
-      <c r="F31" s="150"/>
-    </row>
-    <row r="32" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A32" s="82"/>
-      <c r="B32" s="74">
-        <v>4</v>
-      </c>
-      <c r="C32" s="135" t="s">
+      <c r="C35" s="144" t="s">
+        <v>117</v>
+      </c>
+      <c r="D35" s="145"/>
+      <c r="E35" s="145"/>
+      <c r="F35" s="146"/>
+      <c r="G35" s="123" t="s">
         <v>106</v>
       </c>
-      <c r="D32" s="122"/>
-      <c r="E32" s="122"/>
-      <c r="F32" s="123"/>
-    </row>
-    <row r="33" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A33" s="82"/>
-      <c r="B33" s="72">
-        <v>5</v>
-      </c>
-      <c r="C33" s="135" t="s">
-        <v>106</v>
-      </c>
-      <c r="D33" s="122"/>
-      <c r="E33" s="122"/>
-      <c r="F33" s="123"/>
-    </row>
-    <row r="34" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A34" s="82"/>
-      <c r="B34" s="72">
-        <v>6</v>
-      </c>
-      <c r="C34" s="135" t="s">
-        <v>106</v>
-      </c>
-      <c r="D34" s="122"/>
-      <c r="E34" s="122"/>
-      <c r="F34" s="123"/>
-    </row>
-    <row r="35" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A35" s="89"/>
-      <c r="B35" s="90"/>
-      <c r="C35" s="126"/>
-      <c r="D35" s="127"/>
-      <c r="E35" s="127"/>
-      <c r="F35" s="128"/>
-    </row>
-    <row r="36" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A36" s="87"/>
-      <c r="B36" s="88" t="s">
+    </row>
+    <row r="36" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A36" s="94"/>
+      <c r="B36" s="95"/>
+      <c r="C36" s="155"/>
+      <c r="D36" s="156"/>
+      <c r="E36" s="156"/>
+      <c r="F36" s="157"/>
+      <c r="G36" s="96"/>
+    </row>
+    <row r="37" spans="1:7" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A37" s="92"/>
+      <c r="B37" s="93" t="s">
         <v>87</v>
       </c>
-      <c r="C36" s="129" t="s">
-        <v>100</v>
-      </c>
-      <c r="D36" s="130"/>
-      <c r="E36" s="130"/>
-      <c r="F36" s="131"/>
-    </row>
-    <row r="37" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A37" s="83"/>
-      <c r="B37" s="78" t="s">
+      <c r="C37" s="158" t="s">
+        <v>108</v>
+      </c>
+      <c r="D37" s="159"/>
+      <c r="E37" s="159"/>
+      <c r="F37" s="160"/>
+      <c r="G37" s="128" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A38" s="88"/>
+      <c r="B38" s="82" t="s">
         <v>87</v>
       </c>
-      <c r="C37" s="110" t="s">
-        <v>130</v>
-      </c>
-      <c r="D37" s="111"/>
-      <c r="E37" s="111"/>
-      <c r="F37" s="112"/>
-    </row>
-    <row r="38" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A38" s="52"/>
-      <c r="B38" s="52" t="s">
-        <v>14</v>
-      </c>
-      <c r="C38" s="52"/>
-      <c r="D38" s="52"/>
-      <c r="E38" s="52" t="s">
-        <v>17</v>
-      </c>
-      <c r="F38" s="52"/>
-    </row>
-    <row r="39" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="C38" s="152" t="s">
+        <v>147</v>
+      </c>
+      <c r="D38" s="153"/>
+      <c r="E38" s="153"/>
+      <c r="F38" s="154"/>
+      <c r="G38" s="126" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A39" s="52"/>
       <c r="B39" s="52" t="s">
-        <v>90</v>
+        <v>14</v>
       </c>
       <c r="C39" s="52"/>
       <c r="D39" s="52"/>
       <c r="E39" s="52" t="s">
-        <v>111</v>
+        <v>17</v>
       </c>
       <c r="F39" s="52"/>
+      <c r="G39" s="52"/>
+    </row>
+    <row r="40" spans="1:7" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A40" s="52"/>
+      <c r="B40" s="52" t="s">
+        <v>95</v>
+      </c>
+      <c r="C40" s="52"/>
+      <c r="D40" s="52"/>
+      <c r="E40" s="52" t="s">
+        <v>122</v>
+      </c>
+      <c r="F40" s="52"/>
+      <c r="G40" s="52"/>
     </row>
   </sheetData>
-  <mergeCells count="30">
-    <mergeCell ref="C35:F35"/>
-    <mergeCell ref="C36:F36"/>
-    <mergeCell ref="C37:F37"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="C31:F31"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="C34:F34"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="C18:F18"/>
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C26:F26"/>
-    <mergeCell ref="C27:F27"/>
+  <mergeCells count="31">
     <mergeCell ref="C17:F17"/>
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="C8:E8"/>
@@ -3394,6 +3680,27 @@
     <mergeCell ref="C16:F16"/>
     <mergeCell ref="C11:F11"/>
     <mergeCell ref="C12:F12"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C36:F36"/>
+    <mergeCell ref="C37:F37"/>
+    <mergeCell ref="C38:F38"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="C35:F35"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E5">
@@ -3411,7 +3718,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J40"/>
+  <dimension ref="A1:K40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.85546875" customWidth="1"/>
@@ -3419,63 +3726,68 @@
     <col min="3" max="3" width="20" customWidth="1"/>
     <col min="4" max="4" width="17.140625" customWidth="1"/>
     <col min="5" max="6" width="18.5703125" customWidth="1"/>
+    <col min="7" max="7" width="18.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18.75" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A1" s="51" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="104"/>
-      <c r="C1" s="104"/>
-      <c r="D1" s="104"/>
-      <c r="E1" s="104"/>
-      <c r="F1" s="105" t="s">
+      <c r="B1" s="111"/>
+      <c r="C1" s="111"/>
+      <c r="D1" s="111"/>
+      <c r="E1" s="111"/>
+      <c r="F1" s="112" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" ht="18.75" x14ac:dyDescent="0.35">
+      <c r="G1" s="52"/>
+    </row>
+    <row r="2" spans="1:11" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A2" s="51" t="s">
-        <v>107</v>
-      </c>
-      <c r="B2" s="104"/>
-      <c r="C2" s="104"/>
-      <c r="D2" s="104"/>
-      <c r="E2" s="104"/>
-      <c r="F2" s="105" t="s">
+        <v>118</v>
+      </c>
+      <c r="B2" s="111"/>
+      <c r="C2" s="111"/>
+      <c r="D2" s="111"/>
+      <c r="E2" s="111"/>
+      <c r="F2" s="112" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" ht="18.75" x14ac:dyDescent="0.35">
+      <c r="G2" s="52"/>
+    </row>
+    <row r="3" spans="1:11" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A3" s="51" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="104"/>
-      <c r="C3" s="104"/>
-      <c r="D3" s="104"/>
-      <c r="E3" s="104"/>
-      <c r="F3" s="105" t="s">
+      <c r="B3" s="111"/>
+      <c r="C3" s="111"/>
+      <c r="D3" s="111"/>
+      <c r="E3" s="111"/>
+      <c r="F3" s="112" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="G3" s="52"/>
+    </row>
+    <row r="4" spans="1:11" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A4" s="53" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="B4" s="54"/>
       <c r="C4" s="54"/>
       <c r="D4" s="55"/>
       <c r="E4" s="54"/>
-      <c r="F4" s="106" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="F4" s="113" t="s">
+        <v>123</v>
+      </c>
+      <c r="G4" s="52"/>
+    </row>
+    <row r="5" spans="1:11" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A5" s="56" t="s">
         <v>2</v>
       </c>
       <c r="B5" s="52"/>
       <c r="C5" s="57" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="D5" s="57"/>
       <c r="E5" s="58" t="s">
@@ -3484,55 +3796,59 @@
       <c r="F5" s="59" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="G5" s="52"/>
+    </row>
+    <row r="6" spans="1:11" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A6" s="60" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="52"/>
-      <c r="C6" s="84" t="s">
+      <c r="C6" s="89" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="84"/>
-      <c r="E6" s="85">
+      <c r="D6" s="89"/>
+      <c r="E6" s="90">
         <v>3</v>
       </c>
       <c r="F6" s="59" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="G6" s="52"/>
+    </row>
+    <row r="7" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="61" t="s">
         <v>26</v>
       </c>
       <c r="B7" s="52"/>
-      <c r="C7" s="146" t="s">
+      <c r="C7" s="137" t="s">
         <v>30</v>
       </c>
-      <c r="D7" s="146"/>
-      <c r="E7" s="107" t="s">
+      <c r="D7" s="137"/>
+      <c r="E7" s="114" t="s">
         <v>85</v>
       </c>
       <c r="F7" s="62" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="G7" s="52"/>
+    </row>
+    <row r="8" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A8" s="61" t="s">
         <v>86</v>
       </c>
       <c r="B8" s="52"/>
-      <c r="C8" s="147" t="s">
-        <v>117</v>
-      </c>
-      <c r="D8" s="147"/>
-      <c r="E8" s="147"/>
+      <c r="C8" s="140" t="s">
+        <v>128</v>
+      </c>
+      <c r="D8" s="140"/>
+      <c r="E8" s="140"/>
       <c r="F8" s="62"/>
-      <c r="J8" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="G8" s="52"/>
+      <c r="K8" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="63" t="s">
         <v>19</v>
       </c>
@@ -3545,348 +3861,420 @@
       <c r="D9" s="66"/>
       <c r="E9" s="67"/>
       <c r="F9" s="68"/>
-    </row>
-    <row r="10" spans="1:10" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A10" s="69" t="s">
+      <c r="G9" s="69" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A10" s="70" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="70">
+      <c r="B10" s="71">
+        <v>1</v>
+      </c>
+      <c r="C10" s="185" t="s">
+        <v>163</v>
+      </c>
+      <c r="D10" s="186"/>
+      <c r="E10" s="186"/>
+      <c r="F10" s="187"/>
+      <c r="G10" s="120" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A11" s="73"/>
+      <c r="B11" s="74">
         <v>3</v>
       </c>
-      <c r="C10" s="154" t="s">
-        <v>153</v>
-      </c>
-      <c r="D10" s="155"/>
-      <c r="E10" s="155"/>
-      <c r="F10" s="156"/>
-    </row>
-    <row r="11" spans="1:10" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A11" s="71"/>
-      <c r="B11" s="72">
+      <c r="C11" s="144" t="s">
+        <v>172</v>
+      </c>
+      <c r="D11" s="145"/>
+      <c r="E11" s="145"/>
+      <c r="F11" s="146"/>
+      <c r="G11" s="129" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="73"/>
+      <c r="B12" s="74">
         <v>4</v>
       </c>
-      <c r="C11" s="135" t="s">
-        <v>154</v>
-      </c>
-      <c r="D11" s="122"/>
-      <c r="E11" s="122"/>
-      <c r="F11" s="123"/>
-    </row>
-    <row r="12" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="71"/>
-      <c r="B12" s="72">
+      <c r="C12" s="144" t="s">
+        <v>173</v>
+      </c>
+      <c r="D12" s="145"/>
+      <c r="E12" s="145"/>
+      <c r="F12" s="146"/>
+      <c r="G12" s="129" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A13" s="73"/>
+      <c r="B13" s="74">
         <v>5</v>
       </c>
-      <c r="C12" s="143"/>
-      <c r="D12" s="144"/>
-      <c r="E12" s="144"/>
-      <c r="F12" s="145"/>
-    </row>
-    <row r="13" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="71"/>
-      <c r="B13" s="72">
+      <c r="C13" s="188"/>
+      <c r="D13" s="189"/>
+      <c r="E13" s="189"/>
+      <c r="F13" s="190"/>
+      <c r="G13" s="76"/>
+    </row>
+    <row r="14" spans="1:11" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A14" s="70" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="71" t="s">
+        <v>158</v>
+      </c>
+      <c r="C14" s="191" t="s">
+        <v>159</v>
+      </c>
+      <c r="D14" s="192"/>
+      <c r="E14" s="192"/>
+      <c r="F14" s="193"/>
+      <c r="G14" s="72"/>
+    </row>
+    <row r="15" spans="1:11" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A15" s="73"/>
+      <c r="B15" s="78">
+        <v>4</v>
+      </c>
+      <c r="C15" s="144" t="s">
+        <v>167</v>
+      </c>
+      <c r="D15" s="145"/>
+      <c r="E15" s="145"/>
+      <c r="F15" s="146"/>
+      <c r="G15" s="122" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A16" s="73"/>
+      <c r="B16" s="74">
+        <v>5</v>
+      </c>
+      <c r="C16" s="144" t="s">
+        <v>167</v>
+      </c>
+      <c r="D16" s="145"/>
+      <c r="E16" s="145"/>
+      <c r="F16" s="146"/>
+      <c r="G16" s="122" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A17" s="81"/>
+      <c r="B17" s="82">
         <v>6</v>
       </c>
-      <c r="C13" s="157"/>
-      <c r="D13" s="158"/>
-      <c r="E13" s="158"/>
-      <c r="F13" s="159"/>
-    </row>
-    <row r="14" spans="1:10" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A14" s="69" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" s="70" t="s">
-        <v>140</v>
-      </c>
-      <c r="C14" s="160" t="s">
-        <v>141</v>
-      </c>
-      <c r="D14" s="161"/>
-      <c r="E14" s="161"/>
-      <c r="F14" s="162"/>
-    </row>
-    <row r="15" spans="1:10" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A15" s="71"/>
-      <c r="B15" s="74">
+      <c r="C17" s="152" t="s">
+        <v>168</v>
+      </c>
+      <c r="D17" s="153"/>
+      <c r="E17" s="153"/>
+      <c r="F17" s="154"/>
+      <c r="G17" s="123" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="70" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" s="71">
+        <v>2</v>
+      </c>
+      <c r="C18" s="141"/>
+      <c r="D18" s="142"/>
+      <c r="E18" s="142"/>
+      <c r="F18" s="143"/>
+      <c r="G18" s="120"/>
+    </row>
+    <row r="19" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="73"/>
+      <c r="B19" s="78">
+        <v>3</v>
+      </c>
+      <c r="C19" s="181" t="s">
+        <v>181</v>
+      </c>
+      <c r="D19" s="182"/>
+      <c r="E19" s="182"/>
+      <c r="F19" s="183"/>
+      <c r="G19" s="133" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="73"/>
+      <c r="B20" s="78">
         <v>4</v>
       </c>
-      <c r="C15" s="135" t="s">
+      <c r="C20" s="144" t="s">
+        <v>164</v>
+      </c>
+      <c r="D20" s="145"/>
+      <c r="E20" s="145"/>
+      <c r="F20" s="146"/>
+      <c r="G20" s="133" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A21" s="73"/>
+      <c r="B21" s="74">
+        <v>5</v>
+      </c>
+      <c r="C21" s="152"/>
+      <c r="D21" s="153"/>
+      <c r="E21" s="153"/>
+      <c r="F21" s="154"/>
+      <c r="G21" s="118"/>
+    </row>
+    <row r="22" spans="1:7" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A22" s="70" t="s">
+        <v>23</v>
+      </c>
+      <c r="B22" s="71">
+        <v>3</v>
+      </c>
+      <c r="C22" s="181" t="s">
+        <v>170</v>
+      </c>
+      <c r="D22" s="182"/>
+      <c r="E22" s="182"/>
+      <c r="F22" s="183"/>
+      <c r="G22" s="122" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="73"/>
+      <c r="B23" s="78">
+        <v>4</v>
+      </c>
+      <c r="C23" s="144" t="s">
+        <v>171</v>
+      </c>
+      <c r="D23" s="145"/>
+      <c r="E23" s="145"/>
+      <c r="F23" s="146"/>
+      <c r="G23" s="122" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A24" s="73"/>
+      <c r="B24" s="74">
+        <v>5</v>
+      </c>
+      <c r="C24" s="144" t="s">
+        <v>180</v>
+      </c>
+      <c r="D24" s="145"/>
+      <c r="E24" s="145"/>
+      <c r="F24" s="146"/>
+      <c r="G24" s="122" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A25" s="81"/>
+      <c r="B25" s="82">
+        <v>6</v>
+      </c>
+      <c r="C25" s="152"/>
+      <c r="D25" s="153"/>
+      <c r="E25" s="153"/>
+      <c r="F25" s="154"/>
+      <c r="G25" s="123"/>
+    </row>
+    <row r="26" spans="1:7" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A26" s="70" t="s">
+        <v>24</v>
+      </c>
+      <c r="B26" s="71">
+        <v>4</v>
+      </c>
+      <c r="C26" s="141"/>
+      <c r="D26" s="142"/>
+      <c r="E26" s="142"/>
+      <c r="F26" s="143"/>
+      <c r="G26" s="72"/>
+    </row>
+    <row r="27" spans="1:7" ht="56.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="83"/>
+      <c r="B27" s="74">
+        <v>5</v>
+      </c>
+      <c r="C27" s="144" t="s">
+        <v>176</v>
+      </c>
+      <c r="D27" s="145"/>
+      <c r="E27" s="145"/>
+      <c r="F27" s="146"/>
+      <c r="G27" s="132" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A28" s="83"/>
+      <c r="B28" s="74">
+        <v>6</v>
+      </c>
+      <c r="C28" s="144" t="s">
+        <v>175</v>
+      </c>
+      <c r="D28" s="145"/>
+      <c r="E28" s="145"/>
+      <c r="F28" s="146"/>
+      <c r="G28" s="122" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="84"/>
+      <c r="B29" s="80">
+        <v>7</v>
+      </c>
+      <c r="C29" s="144" t="s">
+        <v>174</v>
+      </c>
+      <c r="D29" s="145"/>
+      <c r="E29" s="145"/>
+      <c r="F29" s="146"/>
+      <c r="G29" s="122" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="84"/>
+      <c r="B30" s="80">
+        <v>8</v>
+      </c>
+      <c r="C30" s="144" t="s">
+        <v>174</v>
+      </c>
+      <c r="D30" s="145"/>
+      <c r="E30" s="145"/>
+      <c r="F30" s="146"/>
+      <c r="G30" s="122" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A31" s="86" t="s">
+        <v>25</v>
+      </c>
+      <c r="B31" s="71">
+        <v>1</v>
+      </c>
+      <c r="C31" s="158" t="s">
+        <v>165</v>
+      </c>
+      <c r="D31" s="159"/>
+      <c r="E31" s="159"/>
+      <c r="F31" s="160"/>
+      <c r="G31" s="127" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A32" s="87"/>
+      <c r="B32" s="78">
+        <v>2</v>
+      </c>
+      <c r="C32" s="144" t="s">
+        <v>165</v>
+      </c>
+      <c r="D32" s="145"/>
+      <c r="E32" s="145"/>
+      <c r="F32" s="146"/>
+      <c r="G32" s="122" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A33" s="87"/>
+      <c r="B33" s="74">
+        <v>3</v>
+      </c>
+      <c r="C33" s="144" t="s">
+        <v>165</v>
+      </c>
+      <c r="D33" s="145"/>
+      <c r="E33" s="145"/>
+      <c r="F33" s="146"/>
+      <c r="G33" s="123" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A34" s="87"/>
+      <c r="B34" s="74">
+        <v>4</v>
+      </c>
+      <c r="C34" s="200"/>
+      <c r="D34" s="201"/>
+      <c r="E34" s="201"/>
+      <c r="F34" s="202"/>
+      <c r="G34" s="122"/>
+    </row>
+    <row r="35" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A35" s="94"/>
+      <c r="B35" s="95"/>
+      <c r="C35" s="155"/>
+      <c r="D35" s="156"/>
+      <c r="E35" s="156"/>
+      <c r="F35" s="157"/>
+      <c r="G35" s="96"/>
+    </row>
+    <row r="36" spans="1:7" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A36" s="92"/>
+      <c r="B36" s="93" t="s">
+        <v>87</v>
+      </c>
+      <c r="C36" s="158" t="s">
+        <v>162</v>
+      </c>
+      <c r="D36" s="159"/>
+      <c r="E36" s="159"/>
+      <c r="F36" s="160"/>
+      <c r="G36" s="128" t="s">
         <v>148</v>
       </c>
-      <c r="D15" s="122"/>
-      <c r="E15" s="122"/>
-      <c r="F15" s="123"/>
-    </row>
-    <row r="16" spans="1:10" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A16" s="71"/>
-      <c r="B16" s="72">
-        <v>5</v>
-      </c>
-      <c r="C16" s="135" t="s">
-        <v>148</v>
-      </c>
-      <c r="D16" s="122"/>
-      <c r="E16" s="122"/>
-      <c r="F16" s="123"/>
-    </row>
-    <row r="17" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A17" s="77"/>
-      <c r="B17" s="78">
-        <v>6</v>
-      </c>
-      <c r="C17" s="110" t="s">
-        <v>149</v>
-      </c>
-      <c r="D17" s="111"/>
-      <c r="E17" s="111"/>
-      <c r="F17" s="112"/>
-    </row>
-    <row r="18" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="69" t="s">
-        <v>22</v>
-      </c>
-      <c r="B18" s="70">
-        <v>2</v>
-      </c>
-      <c r="C18" s="148"/>
-      <c r="D18" s="149"/>
-      <c r="E18" s="149"/>
-      <c r="F18" s="150"/>
-    </row>
-    <row r="19" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="71"/>
-      <c r="B19" s="74">
-        <v>3</v>
-      </c>
-      <c r="C19" s="174"/>
-      <c r="D19" s="175"/>
-      <c r="E19" s="175"/>
-      <c r="F19" s="176"/>
-    </row>
-    <row r="20" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="71"/>
-      <c r="B20" s="74">
-        <v>4</v>
-      </c>
-      <c r="C20" s="135" t="s">
-        <v>145</v>
-      </c>
-      <c r="D20" s="122"/>
-      <c r="E20" s="122"/>
-      <c r="F20" s="123"/>
-    </row>
-    <row r="21" spans="1:6" ht="55.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A21" s="71"/>
-      <c r="B21" s="72">
-        <v>5</v>
-      </c>
-      <c r="C21" s="110" t="s">
-        <v>157</v>
-      </c>
-      <c r="D21" s="111"/>
-      <c r="E21" s="111"/>
-      <c r="F21" s="112"/>
-    </row>
-    <row r="22" spans="1:6" ht="18.75" x14ac:dyDescent="0.35">
-      <c r="A22" s="69" t="s">
-        <v>23</v>
-      </c>
-      <c r="B22" s="70">
-        <v>3</v>
-      </c>
-      <c r="C22" s="166" t="s">
-        <v>150</v>
-      </c>
-      <c r="D22" s="167"/>
-      <c r="E22" s="167"/>
-      <c r="F22" s="168"/>
-    </row>
-    <row r="23" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="71"/>
-      <c r="B23" s="74">
-        <v>4</v>
-      </c>
-      <c r="C23" s="135" t="s">
-        <v>151</v>
-      </c>
-      <c r="D23" s="122"/>
-      <c r="E23" s="122"/>
-      <c r="F23" s="123"/>
-    </row>
-    <row r="24" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A24" s="71"/>
-      <c r="B24" s="72">
-        <v>5</v>
-      </c>
-      <c r="C24" s="135" t="s">
-        <v>152</v>
-      </c>
-      <c r="D24" s="122"/>
-      <c r="E24" s="122"/>
-      <c r="F24" s="123"/>
-    </row>
-    <row r="25" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A25" s="77"/>
-      <c r="B25" s="78">
-        <v>6</v>
-      </c>
-      <c r="C25" s="110" t="s">
-        <v>146</v>
-      </c>
-      <c r="D25" s="111"/>
-      <c r="E25" s="111"/>
-      <c r="F25" s="112"/>
-    </row>
-    <row r="26" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A26" s="69" t="s">
-        <v>24</v>
-      </c>
-      <c r="B26" s="70">
-        <v>4</v>
-      </c>
-      <c r="C26" s="148"/>
-      <c r="D26" s="149"/>
-      <c r="E26" s="149"/>
-      <c r="F26" s="150"/>
-    </row>
-    <row r="27" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A27" s="79"/>
-      <c r="B27" s="72">
-        <v>5</v>
-      </c>
-      <c r="C27" s="143"/>
-      <c r="D27" s="144"/>
-      <c r="E27" s="144"/>
-      <c r="F27" s="145"/>
-    </row>
-    <row r="28" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A28" s="79"/>
-      <c r="B28" s="72">
-        <v>6</v>
-      </c>
-      <c r="C28" s="135" t="s">
-        <v>156</v>
-      </c>
-      <c r="D28" s="122"/>
-      <c r="E28" s="122"/>
-      <c r="F28" s="123"/>
-    </row>
-    <row r="29" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="80"/>
-      <c r="B29" s="76">
-        <v>7</v>
-      </c>
-      <c r="C29" s="135" t="s">
-        <v>155</v>
-      </c>
-      <c r="D29" s="122"/>
-      <c r="E29" s="122"/>
-      <c r="F29" s="123"/>
-    </row>
-    <row r="30" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="80"/>
-      <c r="B30" s="76">
-        <v>8</v>
-      </c>
-      <c r="C30" s="135" t="s">
-        <v>155</v>
-      </c>
-      <c r="D30" s="122"/>
-      <c r="E30" s="122"/>
-      <c r="F30" s="123"/>
-    </row>
-    <row r="31" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A31" s="81" t="s">
-        <v>25</v>
-      </c>
-      <c r="B31" s="70">
-        <v>1</v>
-      </c>
-      <c r="C31" s="129" t="s">
-        <v>147</v>
-      </c>
-      <c r="D31" s="130"/>
-      <c r="E31" s="130"/>
-      <c r="F31" s="131"/>
-    </row>
-    <row r="32" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A32" s="82"/>
-      <c r="B32" s="74">
-        <v>2</v>
-      </c>
-      <c r="C32" s="135" t="s">
-        <v>147</v>
-      </c>
-      <c r="D32" s="122"/>
-      <c r="E32" s="122"/>
-      <c r="F32" s="123"/>
-    </row>
-    <row r="33" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A33" s="82"/>
-      <c r="B33" s="72">
-        <v>3</v>
-      </c>
-      <c r="C33" s="135" t="s">
-        <v>147</v>
-      </c>
-      <c r="D33" s="122"/>
-      <c r="E33" s="122"/>
-      <c r="F33" s="123"/>
-    </row>
-    <row r="34" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="82"/>
-      <c r="B34" s="72">
-        <v>4</v>
-      </c>
-      <c r="C34" s="174"/>
-      <c r="D34" s="175"/>
-      <c r="E34" s="175"/>
-      <c r="F34" s="176"/>
-    </row>
-    <row r="35" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A35" s="89"/>
-      <c r="B35" s="90"/>
-      <c r="C35" s="126"/>
-      <c r="D35" s="127"/>
-      <c r="E35" s="127"/>
-      <c r="F35" s="128"/>
-    </row>
-    <row r="36" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A36" s="87"/>
-      <c r="B36" s="88" t="s">
+    </row>
+    <row r="37" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A37" s="88"/>
+      <c r="B37" s="82" t="s">
         <v>87</v>
       </c>
-      <c r="C36" s="129" t="s">
-        <v>144</v>
-      </c>
-      <c r="D36" s="130"/>
-      <c r="E36" s="130"/>
-      <c r="F36" s="131"/>
-    </row>
-    <row r="37" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A37" s="83"/>
-      <c r="B37" s="78" t="s">
-        <v>87</v>
-      </c>
-      <c r="C37" s="177"/>
-      <c r="D37" s="178"/>
-      <c r="E37" s="178"/>
-      <c r="F37" s="179"/>
-    </row>
-    <row r="38" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="108" t="s">
-        <v>142</v>
-      </c>
-      <c r="B38" s="109"/>
-      <c r="C38" s="173" t="s">
-        <v>143</v>
-      </c>
-      <c r="D38" s="173"/>
-      <c r="E38" s="173"/>
-      <c r="F38" s="173"/>
-    </row>
-    <row r="39" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="C37" s="197"/>
+      <c r="D37" s="198"/>
+      <c r="E37" s="198"/>
+      <c r="F37" s="199"/>
+      <c r="G37" s="126"/>
+    </row>
+    <row r="38" spans="1:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A38" s="130" t="s">
+        <v>160</v>
+      </c>
+      <c r="B38" s="131"/>
+      <c r="C38" s="203" t="s">
+        <v>161</v>
+      </c>
+      <c r="D38" s="203"/>
+      <c r="E38" s="203"/>
+      <c r="F38" s="203"/>
+      <c r="G38" s="52"/>
+    </row>
+    <row r="39" spans="1:7" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A39" s="52"/>
       <c r="B39" s="52" t="s">
         <v>14</v>
@@ -3897,36 +4285,22 @@
         <v>17</v>
       </c>
       <c r="F39" s="52"/>
-    </row>
-    <row r="40" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="G39" s="52"/>
+    </row>
+    <row r="40" spans="1:7" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A40" s="52"/>
       <c r="B40" s="52" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="C40" s="52"/>
       <c r="D40" s="52"/>
       <c r="E40" s="52" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="F40" s="52"/>
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="C37:F37"/>
-    <mergeCell ref="C31:F31"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="C34:F34"/>
-    <mergeCell ref="C35:F35"/>
-    <mergeCell ref="C36:F36"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C26:F26"/>
     <mergeCell ref="C38:F38"/>
     <mergeCell ref="C18:F18"/>
     <mergeCell ref="C7:D7"/>
@@ -3943,6 +4317,21 @@
     <mergeCell ref="C19:F19"/>
     <mergeCell ref="C20:F20"/>
     <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="C37:F37"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="C36:F36"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C5">
@@ -4039,10 +4428,10 @@
       <c r="A7" s="30" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="227" t="s">
+      <c r="C7" s="204" t="s">
         <v>30</v>
       </c>
-      <c r="D7" s="227"/>
+      <c r="D7" s="204"/>
       <c r="E7" s="29" t="s">
         <v>18</v>
       </c>
@@ -4054,10 +4443,10 @@
       <c r="A8" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="230" t="s">
+      <c r="C8" s="210" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="230"/>
+      <c r="D8" s="210"/>
       <c r="E8" s="29"/>
       <c r="F8" s="7"/>
     </row>
@@ -4079,16 +4468,16 @@
       </c>
     </row>
     <row r="10" spans="1:15" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="213"/>
-      <c r="B10" s="214"/>
-      <c r="C10" s="228" t="s">
+      <c r="A10" s="221"/>
+      <c r="B10" s="222"/>
+      <c r="C10" s="205" t="s">
         <v>27</v>
       </c>
-      <c r="D10" s="229"/>
-      <c r="E10" s="228" t="s">
+      <c r="D10" s="206"/>
+      <c r="E10" s="205" t="s">
         <v>28</v>
       </c>
-      <c r="F10" s="229"/>
+      <c r="F10" s="206"/>
       <c r="G10" s="31"/>
     </row>
     <row r="11" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4098,12 +4487,12 @@
       <c r="B11" s="26">
         <v>3</v>
       </c>
-      <c r="C11" s="208" t="s">
+      <c r="C11" s="223" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="209"/>
-      <c r="E11" s="209"/>
-      <c r="F11" s="210"/>
+      <c r="D11" s="224"/>
+      <c r="E11" s="224"/>
+      <c r="F11" s="225"/>
       <c r="G11" s="41" t="s">
         <v>36</v>
       </c>
@@ -4113,12 +4502,12 @@
       <c r="B12" s="23">
         <v>4</v>
       </c>
-      <c r="C12" s="192" t="s">
+      <c r="C12" s="226" t="s">
         <v>35</v>
       </c>
-      <c r="D12" s="193"/>
-      <c r="E12" s="193"/>
-      <c r="F12" s="211"/>
+      <c r="D12" s="227"/>
+      <c r="E12" s="227"/>
+      <c r="F12" s="228"/>
       <c r="G12" s="42" t="s">
         <v>36</v>
       </c>
@@ -4128,12 +4517,12 @@
       <c r="B13" s="23">
         <v>5</v>
       </c>
-      <c r="C13" s="184" t="s">
+      <c r="C13" s="207" t="s">
         <v>38</v>
       </c>
-      <c r="D13" s="185"/>
-      <c r="E13" s="185"/>
-      <c r="F13" s="186"/>
+      <c r="D13" s="208"/>
+      <c r="E13" s="208"/>
+      <c r="F13" s="209"/>
       <c r="G13" s="42" t="s">
         <v>36</v>
       </c>
@@ -4143,12 +4532,12 @@
       <c r="B14" s="23">
         <v>6</v>
       </c>
-      <c r="C14" s="194"/>
-      <c r="D14" s="195"/>
-      <c r="E14" s="195" t="s">
+      <c r="C14" s="231"/>
+      <c r="D14" s="232"/>
+      <c r="E14" s="232" t="s">
         <v>48</v>
       </c>
-      <c r="F14" s="196"/>
+      <c r="F14" s="233"/>
       <c r="G14" s="43" t="s">
         <v>36</v>
       </c>
@@ -4160,12 +4549,12 @@
       <c r="B15" s="26">
         <v>3</v>
       </c>
-      <c r="C15" s="215" t="s">
+      <c r="C15" s="229" t="s">
         <v>49</v>
       </c>
-      <c r="D15" s="200"/>
-      <c r="E15" s="200"/>
-      <c r="F15" s="201"/>
+      <c r="D15" s="230"/>
+      <c r="E15" s="230"/>
+      <c r="F15" s="247"/>
       <c r="G15" s="41" t="s">
         <v>37</v>
       </c>
@@ -4176,12 +4565,12 @@
       <c r="B16" s="36">
         <v>4</v>
       </c>
-      <c r="C16" s="216" t="s">
+      <c r="C16" s="234" t="s">
         <v>50</v>
       </c>
-      <c r="D16" s="202"/>
-      <c r="E16" s="202"/>
-      <c r="F16" s="203"/>
+      <c r="D16" s="235"/>
+      <c r="E16" s="235"/>
+      <c r="F16" s="248"/>
       <c r="G16" s="42" t="s">
         <v>37</v>
       </c>
@@ -4192,12 +4581,12 @@
       <c r="B17" s="23">
         <v>5</v>
       </c>
-      <c r="C17" s="184" t="s">
+      <c r="C17" s="207" t="s">
         <v>51</v>
       </c>
-      <c r="D17" s="185"/>
-      <c r="E17" s="185"/>
-      <c r="F17" s="186"/>
+      <c r="D17" s="208"/>
+      <c r="E17" s="208"/>
+      <c r="F17" s="209"/>
       <c r="G17" s="44" t="s">
         <v>41</v>
       </c>
@@ -4207,14 +4596,14 @@
       <c r="B18" s="33">
         <v>6</v>
       </c>
-      <c r="C18" s="184" t="s">
+      <c r="C18" s="207" t="s">
         <v>73</v>
       </c>
-      <c r="D18" s="185"/>
-      <c r="E18" s="185" t="s">
+      <c r="D18" s="208"/>
+      <c r="E18" s="208" t="s">
         <v>74</v>
       </c>
-      <c r="F18" s="186"/>
+      <c r="F18" s="209"/>
       <c r="G18" s="45" t="s">
         <v>45</v>
       </c>
@@ -4224,12 +4613,12 @@
       <c r="B19" s="33">
         <v>7</v>
       </c>
-      <c r="C19" s="187"/>
-      <c r="D19" s="188"/>
-      <c r="E19" s="182" t="s">
+      <c r="C19" s="250"/>
+      <c r="D19" s="251"/>
+      <c r="E19" s="241" t="s">
         <v>52</v>
       </c>
-      <c r="F19" s="183"/>
+      <c r="F19" s="238"/>
       <c r="G19" s="46" t="s">
         <v>42</v>
       </c>
@@ -4239,12 +4628,12 @@
       <c r="B20" s="24">
         <v>8</v>
       </c>
-      <c r="C20" s="198"/>
-      <c r="D20" s="199"/>
-      <c r="E20" s="199" t="s">
+      <c r="C20" s="245"/>
+      <c r="D20" s="246"/>
+      <c r="E20" s="246" t="s">
         <v>53</v>
       </c>
-      <c r="F20" s="204"/>
+      <c r="F20" s="249"/>
       <c r="G20" s="47" t="s">
         <v>42</v>
       </c>
@@ -4256,10 +4645,10 @@
       <c r="B21" s="26">
         <v>1</v>
       </c>
-      <c r="C21" s="208"/>
-      <c r="D21" s="209"/>
-      <c r="E21" s="209"/>
-      <c r="F21" s="210"/>
+      <c r="C21" s="223"/>
+      <c r="D21" s="224"/>
+      <c r="E21" s="224"/>
+      <c r="F21" s="225"/>
       <c r="G21" s="41"/>
     </row>
     <row r="22" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4267,12 +4656,12 @@
       <c r="B22" s="36">
         <v>2</v>
       </c>
-      <c r="C22" s="192" t="s">
+      <c r="C22" s="226" t="s">
         <v>54</v>
       </c>
-      <c r="D22" s="193"/>
-      <c r="E22" s="193"/>
-      <c r="F22" s="211"/>
+      <c r="D22" s="227"/>
+      <c r="E22" s="227"/>
+      <c r="F22" s="228"/>
       <c r="G22" s="42" t="s">
         <v>41</v>
       </c>
@@ -4282,14 +4671,14 @@
       <c r="B23" s="36">
         <v>3</v>
       </c>
-      <c r="C23" s="184" t="s">
+      <c r="C23" s="207" t="s">
         <v>75</v>
       </c>
-      <c r="D23" s="185"/>
-      <c r="E23" s="185" t="s">
+      <c r="D23" s="208"/>
+      <c r="E23" s="208" t="s">
         <v>76</v>
       </c>
-      <c r="F23" s="186"/>
+      <c r="F23" s="209"/>
       <c r="G23" s="42" t="s">
         <v>44</v>
       </c>
@@ -4299,12 +4688,12 @@
       <c r="B24" s="36">
         <v>4</v>
       </c>
-      <c r="C24" s="192"/>
-      <c r="D24" s="193"/>
-      <c r="E24" s="185" t="s">
+      <c r="C24" s="226"/>
+      <c r="D24" s="227"/>
+      <c r="E24" s="208" t="s">
         <v>55</v>
       </c>
-      <c r="F24" s="186"/>
+      <c r="F24" s="209"/>
       <c r="G24" s="42" t="s">
         <v>33</v>
       </c>
@@ -4314,12 +4703,12 @@
       <c r="B25" s="36">
         <v>5</v>
       </c>
-      <c r="C25" s="192"/>
-      <c r="D25" s="193"/>
-      <c r="E25" s="185" t="s">
+      <c r="C25" s="226"/>
+      <c r="D25" s="227"/>
+      <c r="E25" s="208" t="s">
         <v>56</v>
       </c>
-      <c r="F25" s="186"/>
+      <c r="F25" s="209"/>
       <c r="G25" s="42" t="s">
         <v>33</v>
       </c>
@@ -4330,12 +4719,12 @@
       <c r="B26" s="23">
         <v>6</v>
       </c>
-      <c r="C26" s="194"/>
-      <c r="D26" s="195"/>
-      <c r="E26" s="195" t="s">
+      <c r="C26" s="231"/>
+      <c r="D26" s="232"/>
+      <c r="E26" s="232" t="s">
         <v>58</v>
       </c>
-      <c r="F26" s="196"/>
+      <c r="F26" s="233"/>
       <c r="G26" s="47" t="s">
         <v>46</v>
       </c>
@@ -4348,12 +4737,12 @@
       <c r="B27" s="26">
         <v>1</v>
       </c>
-      <c r="C27" s="189" t="s">
+      <c r="C27" s="252" t="s">
         <v>63</v>
       </c>
-      <c r="D27" s="190"/>
-      <c r="E27" s="190"/>
-      <c r="F27" s="191"/>
+      <c r="D27" s="253"/>
+      <c r="E27" s="253"/>
+      <c r="F27" s="254"/>
       <c r="G27" s="41" t="s">
         <v>37</v>
       </c>
@@ -4363,12 +4752,12 @@
       <c r="B28" s="36">
         <v>2</v>
       </c>
-      <c r="C28" s="180" t="s">
+      <c r="C28" s="236" t="s">
         <v>59</v>
       </c>
-      <c r="D28" s="212"/>
-      <c r="E28" s="212"/>
-      <c r="F28" s="183"/>
+      <c r="D28" s="237"/>
+      <c r="E28" s="237"/>
+      <c r="F28" s="238"/>
       <c r="G28" s="42" t="s">
         <v>37</v>
       </c>
@@ -4378,14 +4767,14 @@
       <c r="B29" s="23">
         <v>3</v>
       </c>
-      <c r="C29" s="184" t="s">
+      <c r="C29" s="207" t="s">
         <v>40</v>
       </c>
-      <c r="D29" s="185"/>
-      <c r="E29" s="185" t="s">
+      <c r="D29" s="208"/>
+      <c r="E29" s="208" t="s">
         <v>61</v>
       </c>
-      <c r="F29" s="186"/>
+      <c r="F29" s="209"/>
       <c r="G29" s="48" t="s">
         <v>47</v>
       </c>
@@ -4395,14 +4784,14 @@
       <c r="B30" s="23">
         <v>4</v>
       </c>
-      <c r="C30" s="184" t="s">
+      <c r="C30" s="207" t="s">
         <v>40</v>
       </c>
-      <c r="D30" s="185"/>
-      <c r="E30" s="185" t="s">
+      <c r="D30" s="208"/>
+      <c r="E30" s="208" t="s">
         <v>62</v>
       </c>
-      <c r="F30" s="186"/>
+      <c r="F30" s="209"/>
       <c r="G30" s="49" t="s">
         <v>47</v>
       </c>
@@ -4412,12 +4801,12 @@
       <c r="B31" s="23">
         <v>5</v>
       </c>
-      <c r="C31" s="184" t="s">
+      <c r="C31" s="207" t="s">
         <v>60</v>
       </c>
-      <c r="D31" s="185"/>
-      <c r="E31" s="185"/>
-      <c r="F31" s="186"/>
+      <c r="D31" s="208"/>
+      <c r="E31" s="208"/>
+      <c r="F31" s="209"/>
       <c r="G31" s="43" t="s">
         <v>37</v>
       </c>
@@ -4427,10 +4816,10 @@
       <c r="B32" s="24">
         <v>6</v>
       </c>
-      <c r="C32" s="194"/>
-      <c r="D32" s="195"/>
-      <c r="E32" s="195"/>
-      <c r="F32" s="196"/>
+      <c r="C32" s="231"/>
+      <c r="D32" s="232"/>
+      <c r="E32" s="232"/>
+      <c r="F32" s="233"/>
       <c r="G32" s="43"/>
     </row>
     <row r="33" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4440,14 +4829,14 @@
       <c r="B33" s="26">
         <v>2</v>
       </c>
-      <c r="C33" s="189" t="s">
+      <c r="C33" s="252" t="s">
         <v>65</v>
       </c>
-      <c r="D33" s="197"/>
-      <c r="E33" s="197" t="s">
+      <c r="D33" s="239"/>
+      <c r="E33" s="239" t="s">
         <v>40</v>
       </c>
-      <c r="F33" s="205"/>
+      <c r="F33" s="240"/>
       <c r="G33" s="41" t="s">
         <v>66</v>
       </c>
@@ -4457,14 +4846,14 @@
       <c r="B34" s="23">
         <v>3</v>
       </c>
-      <c r="C34" s="184" t="s">
+      <c r="C34" s="207" t="s">
         <v>57</v>
       </c>
-      <c r="D34" s="185"/>
-      <c r="E34" s="185" t="s">
+      <c r="D34" s="208"/>
+      <c r="E34" s="208" t="s">
         <v>40</v>
       </c>
-      <c r="F34" s="186"/>
+      <c r="F34" s="209"/>
       <c r="G34" s="43" t="s">
         <v>66</v>
       </c>
@@ -4474,12 +4863,12 @@
       <c r="B35" s="23">
         <v>4</v>
       </c>
-      <c r="C35" s="184" t="s">
+      <c r="C35" s="207" t="s">
         <v>72</v>
       </c>
-      <c r="D35" s="185"/>
-      <c r="E35" s="185"/>
-      <c r="F35" s="186"/>
+      <c r="D35" s="208"/>
+      <c r="E35" s="208"/>
+      <c r="F35" s="209"/>
       <c r="G35" s="43" t="s">
         <v>37</v>
       </c>
@@ -4489,12 +4878,12 @@
       <c r="B36" s="33">
         <v>5</v>
       </c>
-      <c r="C36" s="182" t="s">
+      <c r="C36" s="241" t="s">
         <v>77</v>
       </c>
-      <c r="D36" s="181"/>
-      <c r="E36" s="206"/>
-      <c r="F36" s="207"/>
+      <c r="D36" s="242"/>
+      <c r="E36" s="243"/>
+      <c r="F36" s="244"/>
       <c r="G36" s="50" t="s">
         <v>39</v>
       </c>
@@ -4504,12 +4893,12 @@
       <c r="B37" s="33">
         <v>6</v>
       </c>
-      <c r="C37" s="223" t="s">
+      <c r="C37" s="217" t="s">
         <v>77</v>
       </c>
-      <c r="D37" s="224"/>
-      <c r="E37" s="225"/>
-      <c r="F37" s="226"/>
+      <c r="D37" s="218"/>
+      <c r="E37" s="219"/>
+      <c r="F37" s="220"/>
       <c r="G37" s="50" t="s">
         <v>39</v>
       </c>
@@ -4521,12 +4910,12 @@
       <c r="B38" s="26">
         <v>1</v>
       </c>
-      <c r="C38" s="222"/>
-      <c r="D38" s="220"/>
-      <c r="E38" s="220" t="s">
+      <c r="C38" s="216"/>
+      <c r="D38" s="214"/>
+      <c r="E38" s="214" t="s">
         <v>79</v>
       </c>
-      <c r="F38" s="221"/>
+      <c r="F38" s="215"/>
       <c r="G38" s="41" t="s">
         <v>39</v>
       </c>
@@ -4536,14 +4925,14 @@
       <c r="B39" s="36">
         <v>2</v>
       </c>
-      <c r="C39" s="180" t="s">
+      <c r="C39" s="236" t="s">
         <v>67</v>
       </c>
-      <c r="D39" s="181"/>
-      <c r="E39" s="182" t="s">
+      <c r="D39" s="242"/>
+      <c r="E39" s="241" t="s">
         <v>80</v>
       </c>
-      <c r="F39" s="183"/>
+      <c r="F39" s="238"/>
       <c r="G39" s="42" t="s">
         <v>78</v>
       </c>
@@ -4553,14 +4942,14 @@
       <c r="B40" s="23">
         <v>3</v>
       </c>
-      <c r="C40" s="184" t="s">
+      <c r="C40" s="207" t="s">
         <v>64</v>
       </c>
-      <c r="D40" s="185"/>
-      <c r="E40" s="185" t="s">
+      <c r="D40" s="208"/>
+      <c r="E40" s="208" t="s">
         <v>81</v>
       </c>
-      <c r="F40" s="186"/>
+      <c r="F40" s="209"/>
       <c r="G40" s="43" t="s">
         <v>71</v>
       </c>
@@ -4570,14 +4959,14 @@
       <c r="B41" s="23">
         <v>4</v>
       </c>
-      <c r="C41" s="184" t="s">
+      <c r="C41" s="207" t="s">
         <v>43</v>
       </c>
-      <c r="D41" s="185"/>
-      <c r="E41" s="185" t="s">
+      <c r="D41" s="208"/>
+      <c r="E41" s="208" t="s">
         <v>68</v>
       </c>
-      <c r="F41" s="186"/>
+      <c r="F41" s="209"/>
       <c r="G41" s="43" t="s">
         <v>69</v>
       </c>
@@ -4587,14 +4976,14 @@
       <c r="B42" s="33">
         <v>5</v>
       </c>
-      <c r="C42" s="184" t="s">
+      <c r="C42" s="207" t="s">
         <v>68</v>
       </c>
-      <c r="D42" s="185"/>
-      <c r="E42" s="185" t="s">
+      <c r="D42" s="208"/>
+      <c r="E42" s="208" t="s">
         <v>43</v>
       </c>
-      <c r="F42" s="186"/>
+      <c r="F42" s="209"/>
       <c r="G42" s="50" t="s">
         <v>70</v>
       </c>
@@ -4602,10 +4991,10 @@
     <row r="43" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="35"/>
       <c r="B43" s="24"/>
-      <c r="C43" s="217"/>
-      <c r="D43" s="218"/>
-      <c r="E43" s="218"/>
-      <c r="F43" s="219"/>
+      <c r="C43" s="211"/>
+      <c r="D43" s="212"/>
+      <c r="E43" s="212"/>
+      <c r="F43" s="213"/>
       <c r="G43" s="47"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -4626,11 +5015,49 @@
     </row>
   </sheetData>
   <mergeCells count="64">
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="C13:F13"/>
-    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="E39:F39"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="E36:F36"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="C16:D16"/>
     <mergeCell ref="C43:D43"/>
     <mergeCell ref="E43:F43"/>
     <mergeCell ref="C31:D31"/>
@@ -4647,49 +5074,11 @@
     <mergeCell ref="E42:F42"/>
     <mergeCell ref="C37:D37"/>
     <mergeCell ref="E37:F37"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="C17:F17"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="C35:F35"/>
-    <mergeCell ref="E32:F32"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="E36:F36"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="E39:F39"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="C8:D8"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E5">
